--- a/template/2026.1.7/净值.xlsx
+++ b/template/2026.1.7/净值.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22188" windowHeight="9060" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="量化二-结算数据" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,11 +18,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.00000_ "/>
     <numFmt numFmtId="165" formatCode="0.0000%"/>
     <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -627,7 +628,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -639,6 +640,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -647,6 +649,7 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1025,12 +1028,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
-    <col width="11.6666666666667" customWidth="1" style="1" min="1" max="1"/>
-    <col width="15.1111111111111" customWidth="1" style="5" min="2" max="2"/>
-    <col width="15.1111111111111" customWidth="1" style="6" min="3" max="3"/>
-    <col width="15.1111111111111" customWidth="1" style="1" min="4" max="5"/>
+    <col width="11.6636363636364" customWidth="1" style="1" min="1" max="1"/>
+    <col width="15.1090909090909" customWidth="1" style="6" min="2" max="2"/>
+    <col width="15.1090909090909" customWidth="1" style="7" min="3" max="3"/>
+    <col width="15.1090909090909" customWidth="1" style="1" min="4" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1061,13 +1064,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="8" t="n">
         <v>46023</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1075,14 +1078,14 @@
       <c r="D2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>2026/01/05</t>
         </is>
@@ -1105,7 +1108,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>2026/01/06</t>
         </is>
@@ -1128,23 +1131,23 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>2026/01/07</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="0" t="n">
         <v>0.99468</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>-0.5321%</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="0" t="n">
         <v>0.99468</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>-0.5321%</t>
         </is>
@@ -1163,12 +1166,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
-    <col width="11.6666666666667" customWidth="1" style="1" min="1" max="1"/>
-    <col width="15.1111111111111" customWidth="1" style="5" min="2" max="2"/>
-    <col width="15.1111111111111" customWidth="1" style="6" min="3" max="3"/>
-    <col width="15.1111111111111" customWidth="1" style="1" min="4" max="5"/>
+    <col width="11.6636363636364" customWidth="1" style="1" min="1" max="1"/>
+    <col width="15.1090909090909" customWidth="1" style="6" min="2" max="2"/>
+    <col width="15.1090909090909" customWidth="1" style="7" min="3" max="3"/>
+    <col width="15.1090909090909" customWidth="1" style="1" min="4" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1199,13 +1202,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="8" t="n">
         <v>46023</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1213,14 +1216,14 @@
       <c r="D2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>2026/01/05</t>
         </is>
@@ -1243,7 +1246,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>2026/01/06</t>
         </is>
@@ -1266,23 +1269,23 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>2026/01/07</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="0" t="n">
         <v>0.99703</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>-0.3256%</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="0" t="n">
         <v>0.99703</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>-0.3256%</t>
         </is>
@@ -1301,12 +1304,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13" customHeight="1" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13" customHeight="1" outlineLevelRow="4"/>
   <cols>
-    <col width="11.6666666666667" customWidth="1" style="1" min="1" max="1"/>
-    <col width="15.1111111111111" customWidth="1" style="5" min="2" max="2"/>
-    <col width="15.1111111111111" customWidth="1" style="6" min="3" max="3"/>
-    <col width="15.1111111111111" customWidth="1" style="1" min="4" max="5"/>
+    <col width="11.6636363636364" customWidth="1" style="1" min="1" max="1"/>
+    <col width="15.1090909090909" customWidth="1" style="6" min="2" max="2"/>
+    <col width="15.1090909090909" customWidth="1" style="7" min="3" max="3"/>
+    <col width="15.1090909090909" customWidth="1" style="1" min="4" max="5"/>
   </cols>
   <sheetData>
     <row r="1" s="1">
@@ -1337,13 +1340,13 @@
       </c>
     </row>
     <row r="2" s="1">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="8" t="n">
         <v>46023</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1351,14 +1354,14 @@
       <c r="D2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" s="1">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>2026/01/05</t>
         </is>
@@ -1380,8 +1383,8 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="4" s="1">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>2026/01/06</t>
         </is>
@@ -1403,24 +1406,24 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="5" s="1">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>2026/01/07</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="0" t="n">
         <v>1.00148</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="0" t="n">
         <v>1.00147</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1439,12 +1442,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
-    <col width="11.6666666666667" customWidth="1" style="1" min="1" max="1"/>
-    <col width="15.1111111111111" customWidth="1" style="5" min="2" max="2"/>
-    <col width="15.1111111111111" customWidth="1" style="6" min="3" max="3"/>
-    <col width="15.1111111111111" customWidth="1" style="1" min="4" max="5"/>
+    <col width="11.6636363636364" customWidth="1" style="1" min="1" max="1"/>
+    <col width="15.1090909090909" customWidth="1" style="6" min="2" max="2"/>
+    <col width="15.1090909090909" customWidth="1" style="7" min="3" max="3"/>
+    <col width="15.1090909090909" customWidth="1" style="1" min="4" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1475,13 +1478,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="8" t="n">
         <v>46023</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1489,14 +1492,14 @@
       <c r="D2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>2026/01/05</t>
         </is>
@@ -1519,7 +1522,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>2026/01/06</t>
         </is>
@@ -1542,23 +1545,23 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>2026/01/07</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="0" t="n">
         <v>1.00148</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="0" t="n">
         <v>1.00147</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
